--- a/naver_상품등록_템플릿.xlsx
+++ b/naver_상품등록_템플릿.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1781,6 +1781,317 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>UniFi Cloud Gateway Industrial UCG-Industrial</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>유니파이 클라우드 게이트웨이 인더스트리얼</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;유무선공유기</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>50003150</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1321200</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>UniFi Cloud Gateway Industrial</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ucg-industrial</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>UniFi Switch Enterprise 8 PoE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 엔터프라이즈 8 PoE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1075300</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UniFi Enterprise 8 PoE (Vintage)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>usw-enterprise-8-poe</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>UniFi Switch Flex</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 플렉스</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>194500</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>UniFi Flex</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>usw-flex</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>UniFi Flex Utility</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>유니파이 플렉스 유틸리티</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100800</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>UniFi Flex Utility</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>usw-flex-utility</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>NocoDB 기준 품절 (재고 0) - 인클로저 상품, 스위치 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>UniFi Flex Utility Pro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>유니파이 플렉스 유틸리티 프로</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>123800</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>UniFi Flex Utility Pro</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>uacc-flex-utility-pro</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NocoDB 기준 품절 (재고 0) - 인클로저 상품, 스위치 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UniFi Switch Pro 8 PoE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 프로 8 PoE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>789800</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>UniFi Pro 8 PoE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>usw-pro-8-poe</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>UniFi Switch Pro XG 8 PoE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 프로 XG 8 PoE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1119600</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>UniFi Pro XG 8 PoE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>usw-pro-xg-8-poe</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver_상품등록_템플릿.xlsx
+++ b/naver_상품등록_템플릿.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2092,6 +2092,140 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UniFi Switch Pro Max 16</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 프로 맥스 16</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>637700</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>UniFi Pro Max 16</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>usw-pro-max-16</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>UniFi Switch Pro Max 16 PoE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 프로 맥스 16 PoE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>806700</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>UniFi Pro Max 16 PoE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>usw-pro-max-16-poe</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>UniFi Switch Flex XG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>유니파이 스위치 플렉스 XG</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;스위칭허브</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>50001506</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>673300</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>UniFi Flex 10 GbE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>usw-flex-xg</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>재고 0 - 등록 후 update_price_stock.py로 품절 처리</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver_상품등록_템플릿.xlsx
+++ b/naver_상품등록_템플릿.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2226,6 +2226,737 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>UniFi U7 In-Wall</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>유니파이 U7 인월</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>288500</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>UniFi U7 In-Wall</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>u7-iw</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>UniFi AC Pro</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>유니파이 AC 프로</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>290300</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>UniFi AC Pro</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ac-pro</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UniFi Building Bridge XG</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>유니파이 빌딩 브리지 XG</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2281400</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>UniFi Building Bridge XG</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>building-bridge-xg</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>UniFi Device Bridge</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>유니파이 디바이스 브리지</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>194800</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>UniFi Device Bridge</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>device-bridge</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>UniFi Device Bridge Switch</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>유니파이 디바이스 브리지 스위치</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>669600</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>UniFi Device Bridge Switch</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>device-bridge-switch</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UniFi E7 Campus</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>유니파이 E7 캠퍼스</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1789800</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>UniFi E7 Campus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>e7-campus</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UniFi U6 Enterprise</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>유니파이 U6 엔터프라이즈</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>630400</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>UniFi U6 Enterprise</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>u6-enterprise</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UniFi U6 Enterprise In-Wall</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>유니파이 U6 엔터프라이즈 인월</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>669300</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>UniFi U6 Enterprise In-Wall</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>u6-enterprise-in-wall</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UniFi U6 In-Wall</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>유니파이 U6 인월</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>345500</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UniFi U6 In-Wall</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>u6-in-wall</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UniFi U6 Mesh</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>유니파이 U6 메시</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>346500</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UniFi U6 Mesh</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>u6-mesh</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UniFi U6 Mesh Pro</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>유니파이 U6 메시 프로</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>455400</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>UniFi U6 Mesh Pro</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>u6-mesh-pro</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UniFi U6+</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>유니파이 U6 플러스</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>252000</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>UniFi U6+</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>u6-plus</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UniFi U7 Outdoor</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>유니파이 U7 아웃도어</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>453400</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>UniFi U7 Outdoor</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>u7-outdoor</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro Outdoor</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>유니파이 U7 프로 아웃도어</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>631500</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro Outdoor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>u7-pro-outdoor</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro Wall</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>유니파이 U7 프로 월</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>448200</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro Wall</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>u7-pro-wall</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro XG Wall</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>유니파이 U7 프로 XG 월</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>624500</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro XG Wall</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>u7-pro-xg-wall</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro XGS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>유니파이 U7 프로 XGS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>50001623</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>670700</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>UniFi U7 Pro XGS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>u7-pro-xgs</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver_상품등록_템플릿.xlsx
+++ b/naver_상품등록_템플릿.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2957,6 +2957,682 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UniFi G6 Pro 360</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi G6 Pro 360</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E75" t="n">
+        <v>935700</v>
+      </c>
+      <c r="F75" t="n">
+        <v>935700</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>UniFi G6 Pro 360</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>g6-pro-360</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>UniFi AI PTZ Industrial</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi AI PTZ Industrial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2648900</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2648900</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>UniFi AI PTZ Industrial</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ai-ptz-industrial</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UniFi G5 Turret Ultra</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi G5 Turret Ultra</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E77" t="n">
+        <v>213700</v>
+      </c>
+      <c r="F77" t="n">
+        <v>213700</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>UniFi G5 Turret Ultra</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>g5-turret-ultra</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>UniFi G6 Dome</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi G6 Dome</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E78" t="n">
+        <v>566100</v>
+      </c>
+      <c r="F78" t="n">
+        <v>566100</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UniFi G6 Dome</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>g6-dome</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UniFi AI Theta</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi AI Theta</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E79" t="n">
+        <v>323000</v>
+      </c>
+      <c r="F79" t="n">
+        <v>323000</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UniFi AI Theta</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ai-theta</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>UniFi All-In-One Sensor</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi All-In-One Sensor</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E80" t="n">
+        <v>101800</v>
+      </c>
+      <c r="F80" t="n">
+        <v>101800</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>UniFi All-In-One Sensor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>all-in-one-sensor</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>UniFi Glass Break Sensor</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi Glass Break Sensor</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E81" t="n">
+        <v>101800</v>
+      </c>
+      <c r="F81" t="n">
+        <v>101800</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>UniFi Glass Break Sensor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>glass-break-sensor</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UniFi Motion Sensor</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi Motion Sensor</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E82" t="n">
+        <v>85900</v>
+      </c>
+      <c r="F82" t="n">
+        <v>85900</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UniFi Motion Sensor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>motion-sensor</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UniFi Network Video Recorder Instant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi Network Video Recorder Instant</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E83" t="n">
+        <v>412600</v>
+      </c>
+      <c r="F83" t="n">
+        <v>412600</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>UniFi Network Video Recorder Instant</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>nvr-instant</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UniFi CloudKey+</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi CloudKey+</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E84" t="n">
+        <v>506800</v>
+      </c>
+      <c r="F84" t="n">
+        <v>506800</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>UniFi CloudKey+</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>cloudkey-plus</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UniFi AI Horn Speaker</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi AI Horn Speaker</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E85" t="n">
+        <v>591100</v>
+      </c>
+      <c r="F85" t="n">
+        <v>591100</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>UniFi AI Horn Speaker</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ai-horn-speaker</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UniFi SuperLink Gateway</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi SuperLink Gateway</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E86" t="n">
+        <v>228300</v>
+      </c>
+      <c r="F86" t="n">
+        <v>228300</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UniFi SuperLink Gateway</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>superlink-gateway</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UniFi Floodlight</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi Floodlight</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E87" t="n">
+        <v>166900</v>
+      </c>
+      <c r="F87" t="n">
+        <v>166900</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>UniFi Floodlight</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>floodlight</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Physical Security</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver_상품등록_템플릿.xlsx
+++ b/naver_상품등록_템플릿.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3633,6 +3633,1751 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>UniFi Reader Junction Box</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>UniFi Reader Junction Box</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E88" t="n">
+        <v>66200</v>
+      </c>
+      <c r="F88" t="n">
+        <v>60200</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>UniFi Reader Junction Box</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>reader-junction-box</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Viewer Table Stand</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Viewer Table Stand</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E89" t="n">
+        <v>60800</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Viewer Table Stand</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>intercom-viewer-table-stand</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>5</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>UniFi Gate Hub</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>UniFi Gate Hub</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E90" t="n">
+        <v>624900</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>UniFi Gate Hub</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>gate-hub</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>5</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Flush Mount</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Flush Mount</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E91" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Flush Mount</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>intercom-flush-mount</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>5</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>UniFi Junction Utility</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>UniFi Junction Utility</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E92" t="n">
+        <v>219700</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>UniFi Junction Utility</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>junction-utility</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>5</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>UniFi Magnetic Lock</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UniFi Magnetic Lock</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E93" t="n">
+        <v>271500</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>UniFi Magnetic Lock</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>magnetic-lock</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>5</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>UniFi Gate Starter Kit</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UniFi Gate Starter Kit</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1433700</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>UniFi Gate Starter Kit</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>gate-starter-kit</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>5</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>UniFi Door Hub Mini</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>UniFi Door Hub Mini</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E95" t="n">
+        <v>250700</v>
+      </c>
+      <c r="F95" t="n">
+        <v>212200</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>UniFi Door Hub Mini</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>door-hub-mini</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>5</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Viewer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Viewer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E96" t="n">
+        <v>354400</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Viewer</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>intercom-viewer</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Surface Angle Mount</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Surface Angle Mount</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E97" t="n">
+        <v>95700</v>
+      </c>
+      <c r="F97" t="n">
+        <v>87000</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Surface Angle Mount</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>intercom-surface-angle-mount</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>5</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro Junction Box</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro Junction Box</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E98" t="n">
+        <v>66100</v>
+      </c>
+      <c r="F98" t="n">
+        <v>60100</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro Junction Box</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>reader-pro-junction-box</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>UniFi G6 Entry</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>UniFi G6 Entry</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E99" t="n">
+        <v>557500</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>UniFi G6 Entry</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>g6-entry</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>UniFi G3 Elevator Starter Kit</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>UniFi G3 Elevator Starter Kit</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2044700</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>UniFi G3 Elevator Starter Kit</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>g3-elevator-starter-kit</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>5</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>UniFi Access Button</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>UniFi Access Button</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E101" t="n">
+        <v>78300</v>
+      </c>
+      <c r="F101" t="n">
+        <v>71200</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>UniFi Access Button</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>access-button</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>UniFi Door Lock Relay Cable</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>UniFi Door Lock Relay Cable</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E102" t="n">
+        <v>237000</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>UniFi Door Lock Relay Cable</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>door-lock-relay-cable</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>5</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>UniFi Door Hub</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>UniFi Door Hub</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E103" t="n">
+        <v>448400</v>
+      </c>
+      <c r="F103" t="n">
+        <v>407700</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>UniFi Door Hub</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>door-hub</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>5</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>UniFi Enterprise Access Hub</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>UniFi Enterprise Access Hub</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2203200</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1858800</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>UniFi Enterprise Access Hub</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>enterprise-access-hub</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>5</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>UniFi Access Card (10-Pack)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UniFi Access Card (10-Pack)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E105" t="n">
+        <v>61700</v>
+      </c>
+      <c r="F105" t="n">
+        <v>56100</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>UniFi Access Card</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>access-card-10pack</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>5</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UniFi Pocket Keyfob, 10-Pack</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>UniFi Pocket Keyfob, 10-Pack</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E106" t="n">
+        <v>181800</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>UniFi Pocket Keyfob, 10-Pack</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>pocket-keyfob-10pack</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>5</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Wedge Mount</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Wedge Mount</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E107" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Wedge Mount</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>intercom-wedge-mount</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>5</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Sunshield</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Sunshield</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E108" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>UniFi Intercom Sunshield</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>intercom-sunshield</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>5</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro Angle Mount</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro Angle Mount</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E109" t="n">
+        <v>61800</v>
+      </c>
+      <c r="F109" t="n">
+        <v>56100</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro Angle Mount</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>reader-pro-angle-mount</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>UniFi Door Closer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UniFi Door Closer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E110" t="n">
+        <v>259000</v>
+      </c>
+      <c r="F110" t="n">
+        <v>235500</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>UniFi Door Closer</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>door-closer</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>5</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>UniFi PoE Over 2-Wire Retrofit Extender</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UniFi PoE Over 2-Wire Retrofit Extender</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E111" t="n">
+        <v>194700</v>
+      </c>
+      <c r="F111" t="n">
+        <v>177000</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>UniFi PoE Over 2-Wire Retrofit Extender</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>poe-over-2wire-retrofit-extender</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>5</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E112" t="n">
+        <v>741800</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>UniFi Reader Pro</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>reader-pro</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>5</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>UniFi Retrofit Hub</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UniFi Retrofit Hub</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E113" t="n">
+        <v>514500</v>
+      </c>
+      <c r="F113" t="n">
+        <v>467700</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>UniFi Retrofit Hub</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>retrofit-hub</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>5</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>UniFi Reader Flex</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UniFi Reader Flex</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E114" t="n">
+        <v>446400</v>
+      </c>
+      <c r="F114" t="n">
+        <v>405800</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>UniFi Reader Flex</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>reader-flex</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>5</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>UniFi Panic Bar</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UniFi Panic Bar</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E115" t="n">
+        <v>873600</v>
+      </c>
+      <c r="F115" t="n">
+        <v>794200</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>UniFi Panic Bar</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>panic-bar</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>5</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>UniFi Access Ultra</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UniFi Access Ultra</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E116" t="n">
+        <v>251200</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>UniFi Access Ultra</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>access-ultra</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>5</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UniFi Access Rescue KeySwitch</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UniFi Access Rescue KeySwitch</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E117" t="n">
+        <v>146500</v>
+      </c>
+      <c r="F117" t="n">
+        <v>133200</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>UniFi Access Rescue KeySwitch</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>access-rescue-keyswitch</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>5</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>UniFi Retrofit PSU 12V</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UniFi Retrofit PSU 12V</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Door Access</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E118" t="n">
+        <v>150700</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>UniFi Retrofit PSU 12V</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>retrofit-psu-12v</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>5</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>U5G-Max</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UniFi 5G Max</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E119" t="n">
+        <v>807300</v>
+      </c>
+      <c r="F119" t="n">
+        <v>807300</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>UniFi 5G Max</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>5g-max</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>UC-Cast-Lite</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UniFi Display Cast Lite</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>UniFi Display Cast Lite</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>display-cast-lite</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>U-LTE-Backup Pro</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UniFi LTE Backup Pro</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E121" t="n">
+        <v>527200</v>
+      </c>
+      <c r="F121" t="n">
+        <v>527200</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>UniFi LTE Backup Pro</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>lte-backup-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>UMR</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UniFi Mobile Router</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E122" t="n">
+        <v>324300</v>
+      </c>
+      <c r="F122" t="n">
+        <v>324300</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>UniFi Mobile Router</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>mobile-router</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>UMR-Industrial</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UniFi Mobile Router Industrial</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>UniFi Mobile Router Industrial</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>mobile-router-industrial</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>UMR-Ultra</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UniFi Mobile Router Ultra</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E124" t="n">
+        <v>228300</v>
+      </c>
+      <c r="F124" t="n">
+        <v>228300</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>UniFi Mobile Router Ultra</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>mobile-router-ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>UPL-Port</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UniFi PoE Audio Port</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E125" t="n">
+        <v>406600</v>
+      </c>
+      <c r="F125" t="n">
+        <v>406600</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>UniFi PoE Audio Port</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>poe-audio-port</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>UNAS-2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UniFi UNAS 2</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E126" t="n">
+        <v>415600</v>
+      </c>
+      <c r="F126" t="n">
+        <v>415600</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>UniFi UNAS 2</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>unas-2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver_상품등록_템플릿.xlsx
+++ b/naver_상품등록_템플릿.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5378,6 +5378,170 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>UniFi WiFi BaseStation XG</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>유니파이 와이파이 베이스스테이션 XG</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3311000</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>UniFi WiFi BaseStation XG</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>wifi-basestation-xg</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>UniFi G5 Dome Ultra</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi G5 Dome Ultra</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E128" t="n">
+        <v>249000</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>UniFi G5 Dome Ultra</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>g5-dome-ultra</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>UniFi AirWire</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>유니파이 에어와이어</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>네트워크장비&gt;AP</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>50001623</v>
+      </c>
+      <c r="E129" t="n">
+        <v>444200</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>UniFi AirWire</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>airwire</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>UniFi G5 Pro</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>유니파이 UniFi G5 Pro</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TV/영상가전&gt;CCTV</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>50002707</v>
+      </c>
+      <c r="E130" t="n">
+        <v>836300</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>UniFi G5 Pro</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>g5-pro</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
